--- a/VT_Model_ELC_01.xlsx
+++ b/VT_Model_ELC_01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\labee2\Desktop\PIANIFICAZIONE ENERGETICA\myproject_08_05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3293848F-58A9-419F-A50B-1AE7D0F2EDE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDCAE4C7-5147-4D6F-A9C9-9646344A24F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" tabRatio="901" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9334,9 +9334,9 @@
       <c r="D13" s="116" t="s">
         <v>124</v>
       </c>
-      <c r="E13" s="61" t="str">
-        <f>SEC_Comm!C8</f>
-        <v>ELEC_MV</v>
+      <c r="E13" s="46" t="str">
+        <f>SEC_Comm!C7</f>
+        <v>ELEC_HV</v>
       </c>
       <c r="F13" s="132">
         <v>1</v>

--- a/VT_Model_ELC_01.xlsx
+++ b/VT_Model_ELC_01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\labee2\Desktop\PIANIFICAZIONE ENERGETICA\myproject_08_05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDCAE4C7-5147-4D6F-A9C9-9646344A24F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1760FBB-0A0E-4F23-96FD-51A37009B7BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" tabRatio="901" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" tabRatio="901" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BALANCE" sheetId="138" r:id="rId1"/>
@@ -1155,7 +1155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="352">
   <si>
     <t>Moc osiągalna elektryczna netto</t>
   </si>
@@ -3078,7 +3078,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="238">
+  <cellXfs count="235">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="8" applyFont="1"/>
@@ -3456,11 +3456,8 @@
     <xf numFmtId="0" fontId="34" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="34" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="34" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
@@ -3529,7 +3526,7 @@
     <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="27" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3568,7 +3565,7 @@
     <xf numFmtId="0" fontId="30" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="27" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4507,10 +4504,10 @@
       <c r="C5" s="69"/>
     </row>
     <row r="6" spans="2:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="B6" s="229" t="s">
+      <c r="B6" s="226" t="s">
         <v>183</v>
       </c>
-      <c r="C6" s="232" t="s">
+      <c r="C6" s="229" t="s">
         <v>136</v>
       </c>
       <c r="D6" s="72" t="s">
@@ -4536,8 +4533,8 @@
       </c>
     </row>
     <row r="7" spans="2:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="B7" s="230"/>
-      <c r="C7" s="233"/>
+      <c r="B7" s="227"/>
+      <c r="C7" s="230"/>
       <c r="D7" s="20" t="s">
         <v>137</v>
       </c>
@@ -4561,8 +4558,8 @@
       </c>
     </row>
     <row r="8" spans="2:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B8" s="231"/>
-      <c r="C8" s="234"/>
+      <c r="B8" s="228"/>
+      <c r="C8" s="231"/>
       <c r="D8" s="68" t="s">
         <v>5</v>
       </c>
@@ -4845,10 +4842,10 @@
       <c r="F26" s="69"/>
     </row>
     <row r="27" spans="2:16" ht="31.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="227" t="s">
+      <c r="B27" s="224" t="s">
         <v>213</v>
       </c>
-      <c r="C27" s="225" t="s">
+      <c r="C27" s="222" t="s">
         <v>146</v>
       </c>
       <c r="D27" s="72" t="s">
@@ -4860,8 +4857,8 @@
       <c r="F27" s="69"/>
     </row>
     <row r="28" spans="2:16" ht="31.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="228"/>
-      <c r="C28" s="226"/>
+      <c r="B28" s="225"/>
+      <c r="C28" s="223"/>
       <c r="D28" s="20" t="s">
         <v>149</v>
       </c>
@@ -4988,10 +4985,10 @@
       <c r="F40" s="69"/>
     </row>
     <row r="41" spans="2:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="227" t="s">
+      <c r="B41" s="224" t="s">
         <v>12</v>
       </c>
-      <c r="C41" s="225" t="s">
+      <c r="C41" s="222" t="s">
         <v>146</v>
       </c>
       <c r="D41" s="83" t="s">
@@ -5003,8 +5000,8 @@
       <c r="F41" s="69"/>
     </row>
     <row r="42" spans="2:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="228"/>
-      <c r="C42" s="226"/>
+      <c r="B42" s="225"/>
+      <c r="C42" s="223"/>
       <c r="D42" s="21" t="s">
         <v>24</v>
       </c>
@@ -5624,61 +5621,61 @@
       </c>
     </row>
     <row r="6" spans="2:9" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="B6" s="210" t="s">
+      <c r="B6" s="207" t="s">
         <v>111</v>
       </c>
-      <c r="C6" s="210" t="s">
+      <c r="C6" s="207" t="s">
         <v>129</v>
       </c>
-      <c r="D6" s="224" t="s">
+      <c r="D6" s="234" t="s">
         <v>130</v>
       </c>
-      <c r="E6" s="224"/>
-      <c r="F6" s="224"/>
-      <c r="G6" s="224"/>
+      <c r="E6" s="234"/>
+      <c r="F6" s="234"/>
+      <c r="G6" s="234"/>
     </row>
     <row r="7" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="208" t="str">
+      <c r="B7" s="205" t="str">
         <f>SEC_Processes!D15</f>
         <v>ELE_EX_HC</v>
       </c>
-      <c r="C7" s="207" t="s">
+      <c r="C7" s="204" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="198">
+      <c r="D7" s="195">
         <v>96</v>
       </c>
-      <c r="E7" s="209"/>
-      <c r="F7" s="209"/>
-      <c r="G7" s="209"/>
+      <c r="E7" s="206"/>
+      <c r="F7" s="206"/>
+      <c r="G7" s="206"/>
     </row>
     <row r="8" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="193" t="str">
+      <c r="B8" s="190" t="str">
         <f>SEC_Processes!D16</f>
         <v>ELE_EX_OILGAS</v>
       </c>
-      <c r="C8" s="207" t="s">
+      <c r="C8" s="204" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="194"/>
-      <c r="E8" s="194">
+      <c r="D8" s="191"/>
+      <c r="E8" s="191">
         <v>112</v>
       </c>
-      <c r="F8" s="194"/>
-      <c r="G8" s="194"/>
+      <c r="F8" s="191"/>
+      <c r="G8" s="191"/>
     </row>
     <row r="9" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="211" t="str">
+      <c r="B9" s="208" t="str">
         <f>SEC_Processes!D27</f>
         <v>REFINARY</v>
       </c>
-      <c r="C9" s="214" t="s">
+      <c r="C9" s="211" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="212"/>
-      <c r="E9" s="212"/>
-      <c r="F9" s="212"/>
-      <c r="G9" s="213">
+      <c r="D9" s="209"/>
+      <c r="E9" s="209"/>
+      <c r="F9" s="209"/>
+      <c r="G9" s="210">
         <v>7.3</v>
       </c>
     </row>
@@ -5769,7 +5766,7 @@
       <c r="E5" s="106" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="195" t="s">
+      <c r="F5" s="192" t="s">
         <v>25</v>
       </c>
       <c r="G5" s="106" t="s">
@@ -5945,24 +5942,24 @@
       </c>
     </row>
     <row r="13" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="206" t="s">
+      <c r="B13" s="203" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="206" t="s">
+      <c r="C13" s="203" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="206" t="s">
+      <c r="D13" s="203" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="206" t="s">
+      <c r="E13" s="203" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="206"/>
-      <c r="G13" s="206"/>
-      <c r="H13" s="206" t="s">
+      <c r="F13" s="203"/>
+      <c r="G13" s="203"/>
+      <c r="H13" s="203" t="s">
         <v>40</v>
       </c>
-      <c r="I13" s="206"/>
+      <c r="I13" s="203"/>
     </row>
     <row r="14" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="127" t="s">
@@ -6118,16 +6115,16 @@
       <c r="I24" s="65"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="204" t="s">
+      <c r="B25" s="201" t="s">
         <v>36</v>
       </c>
       <c r="C25" s="42" t="s">
         <v>297</v>
       </c>
-      <c r="D25" s="204" t="s">
+      <c r="D25" s="201" t="s">
         <v>312</v>
       </c>
-      <c r="E25" s="205" t="s">
+      <c r="E25" s="202" t="s">
         <v>38</v>
       </c>
       <c r="F25" s="44"/>
@@ -6154,16 +6151,16 @@
       <c r="I26" s="65"/>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B27" s="204" t="s">
+      <c r="B27" s="201" t="s">
         <v>36</v>
       </c>
       <c r="C27" s="42" t="s">
         <v>302</v>
       </c>
-      <c r="D27" s="204" t="s">
+      <c r="D27" s="201" t="s">
         <v>333</v>
       </c>
-      <c r="E27" s="205" t="s">
+      <c r="E27" s="202" t="s">
         <v>38</v>
       </c>
       <c r="F27" s="44"/>
@@ -6190,7 +6187,7 @@
       <c r="I28" s="65"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B29" s="204" t="s">
+      <c r="B29" s="201" t="s">
         <v>36</v>
       </c>
       <c r="C29" s="42" t="s">
@@ -6199,7 +6196,7 @@
       <c r="D29" s="42" t="s">
         <v>334</v>
       </c>
-      <c r="E29" s="205" t="s">
+      <c r="E29" s="202" t="s">
         <v>38</v>
       </c>
       <c r="F29" s="44"/>
@@ -6226,7 +6223,7 @@
       <c r="I30" s="65"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B31" s="204" t="s">
+      <c r="B31" s="201" t="s">
         <v>36</v>
       </c>
       <c r="C31" s="42" t="s">
@@ -6235,7 +6232,7 @@
       <c r="D31" s="42" t="s">
         <v>315</v>
       </c>
-      <c r="E31" s="205" t="s">
+      <c r="E31" s="202" t="s">
         <v>38</v>
       </c>
       <c r="F31" s="44"/>
@@ -6262,16 +6259,16 @@
       <c r="I32" s="65"/>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B33" s="204" t="s">
+      <c r="B33" s="201" t="s">
         <v>36</v>
       </c>
       <c r="C33" s="42" t="s">
         <v>328</v>
       </c>
-      <c r="D33" s="204" t="s">
+      <c r="D33" s="201" t="s">
         <v>336</v>
       </c>
-      <c r="E33" s="205" t="s">
+      <c r="E33" s="202" t="s">
         <v>38</v>
       </c>
       <c r="F33" s="44"/>
@@ -6298,16 +6295,16 @@
       <c r="I34" s="65"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B35" s="204" t="s">
+      <c r="B35" s="201" t="s">
         <v>36</v>
       </c>
       <c r="C35" s="42" t="s">
         <v>178</v>
       </c>
-      <c r="D35" s="204" t="s">
+      <c r="D35" s="201" t="s">
         <v>179</v>
       </c>
-      <c r="E35" s="205" t="s">
+      <c r="E35" s="202" t="s">
         <v>38</v>
       </c>
       <c r="F35" s="44"/>
@@ -6442,28 +6439,28 @@
       <c r="I42" s="65"/>
     </row>
     <row r="43" spans="2:9" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="215" t="s">
+      <c r="B43" s="212" t="s">
         <v>36</v>
       </c>
-      <c r="C43" s="216" t="s">
+      <c r="C43" s="213" t="s">
         <v>223</v>
       </c>
-      <c r="D43" s="215" t="s">
+      <c r="D43" s="212" t="s">
         <v>223</v>
       </c>
-      <c r="E43" s="217" t="s">
+      <c r="E43" s="214" t="s">
         <v>38</v>
       </c>
-      <c r="F43" s="218"/>
-      <c r="G43" s="218"/>
-      <c r="H43" s="218"/>
-      <c r="I43" s="218"/>
+      <c r="F43" s="215"/>
+      <c r="G43" s="215"/>
+      <c r="H43" s="215"/>
+      <c r="I43" s="215"/>
     </row>
     <row r="47" spans="2:9" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="235" t="s">
+      <c r="B47" s="232" t="s">
         <v>48</v>
       </c>
-      <c r="C47" s="235"/>
+      <c r="C47" s="232"/>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B48" s="99" t="s">
@@ -6624,7 +6621,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="219" t="s">
+      <c r="B7" s="216" t="s">
         <v>239</v>
       </c>
       <c r="C7" s="122" t="s">
@@ -7157,11 +7154,11 @@
       <c r="J29" s="130"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B31" s="236" t="s">
+      <c r="B31" s="233" t="s">
         <v>82</v>
       </c>
-      <c r="C31" s="236"/>
-      <c r="D31" s="236"/>
+      <c r="C31" s="233"/>
+      <c r="D31" s="233"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
@@ -7373,15 +7370,15 @@
       <c r="H4" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="I4" s="237" t="s">
+      <c r="I4" s="221" t="s">
         <v>300</v>
       </c>
-      <c r="J4" s="237"/>
-      <c r="K4" s="237"/>
-      <c r="L4" s="237"/>
-      <c r="M4" s="237"/>
-      <c r="N4" s="237"/>
-      <c r="O4" s="237"/>
+      <c r="J4" s="221"/>
+      <c r="K4" s="221"/>
+      <c r="L4" s="221"/>
+      <c r="M4" s="221"/>
+      <c r="N4" s="221"/>
+      <c r="O4" s="221"/>
       <c r="P4" s="19"/>
       <c r="Q4" s="19" t="s">
         <v>203</v>
@@ -7449,7 +7446,7 @@
       <c r="B6" s="171"/>
       <c r="C6" s="61"/>
       <c r="D6" s="175"/>
-      <c r="E6" s="202" t="s">
+      <c r="E6" s="199" t="s">
         <v>302</v>
       </c>
       <c r="F6" s="173">
@@ -7475,7 +7472,7 @@
       <c r="B7" s="172"/>
       <c r="C7" s="24"/>
       <c r="D7" s="24"/>
-      <c r="E7" s="203" t="s">
+      <c r="E7" s="200" t="s">
         <v>298</v>
       </c>
       <c r="F7" s="174">
@@ -7487,10 +7484,10 @@
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B8" s="199"/>
+      <c r="B8" s="196"/>
       <c r="C8" s="61"/>
       <c r="D8" s="61"/>
-      <c r="E8" s="202" t="s">
+      <c r="E8" s="199" t="s">
         <v>325</v>
       </c>
       <c r="F8" s="173">
@@ -7516,7 +7513,7 @@
       <c r="B9" s="172"/>
       <c r="C9" s="24"/>
       <c r="D9" s="24"/>
-      <c r="E9" s="203" t="s">
+      <c r="E9" s="200" t="s">
         <v>297</v>
       </c>
       <c r="F9" s="174">
@@ -7531,7 +7528,7 @@
       <c r="B10" s="62"/>
       <c r="C10" s="62"/>
       <c r="D10" s="62"/>
-      <c r="E10" s="202" t="s">
+      <c r="E10" s="199" t="s">
         <v>303</v>
       </c>
       <c r="F10" s="173">
@@ -7554,7 +7551,7 @@
       <c r="R10" s="62"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="E11" s="203" t="s">
+      <c r="E11" s="200" t="s">
         <v>314</v>
       </c>
       <c r="F11" s="174">
@@ -7569,7 +7566,7 @@
       <c r="B12" s="62"/>
       <c r="C12" s="62"/>
       <c r="D12" s="62"/>
-      <c r="E12" s="202" t="s">
+      <c r="E12" s="199" t="s">
         <v>315</v>
       </c>
       <c r="F12" s="173">
@@ -7592,7 +7589,7 @@
       <c r="R12" s="62"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="E13" s="203" t="s">
+      <c r="E13" s="200" t="s">
         <v>326</v>
       </c>
       <c r="F13" s="174">
@@ -7607,7 +7604,7 @@
       <c r="B14" s="62"/>
       <c r="C14" s="62"/>
       <c r="D14" s="62"/>
-      <c r="E14" s="223" t="s">
+      <c r="E14" s="220" t="s">
         <v>204</v>
       </c>
       <c r="F14" s="173">
@@ -7633,12 +7630,12 @@
       <c r="B15" s="170"/>
       <c r="C15" s="170"/>
       <c r="D15" s="170"/>
-      <c r="E15" s="200" t="str">
+      <c r="E15" s="197" t="str">
         <f>SEC_Comm!C13</f>
         <v>CO2</v>
       </c>
-      <c r="F15" s="201"/>
-      <c r="G15" s="201"/>
+      <c r="F15" s="198"/>
+      <c r="G15" s="198"/>
       <c r="H15" s="170"/>
       <c r="I15" s="170"/>
       <c r="J15" s="170"/>
@@ -8060,15 +8057,15 @@
       <c r="G6" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="H6" s="237" t="s">
+      <c r="H6" s="221" t="s">
         <v>116</v>
       </c>
-      <c r="I6" s="237"/>
-      <c r="J6" s="237"/>
-      <c r="K6" s="237"/>
-      <c r="L6" s="237"/>
-      <c r="M6" s="237"/>
-      <c r="N6" s="237"/>
+      <c r="I6" s="221"/>
+      <c r="J6" s="221"/>
+      <c r="K6" s="221"/>
+      <c r="L6" s="221"/>
+      <c r="M6" s="221"/>
+      <c r="N6" s="221"/>
       <c r="O6" s="19" t="s">
         <v>117</v>
       </c>
@@ -8789,23 +8786,23 @@
       <c r="O35" s="7"/>
     </row>
     <row r="36" spans="2:15" ht="18.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="196"/>
-      <c r="C36" s="196"/>
-      <c r="D36" s="196"/>
-      <c r="E36" s="196" t="str">
+      <c r="B36" s="193"/>
+      <c r="C36" s="193"/>
+      <c r="D36" s="193"/>
+      <c r="E36" s="193" t="str">
         <f>SEC_Comm!C13</f>
         <v>CO2</v>
       </c>
-      <c r="F36" s="196"/>
-      <c r="G36" s="196"/>
-      <c r="H36" s="196"/>
-      <c r="I36" s="196"/>
-      <c r="J36" s="197"/>
-      <c r="K36" s="196"/>
-      <c r="L36" s="196"/>
-      <c r="M36" s="196"/>
-      <c r="N36" s="196"/>
-      <c r="O36" s="196"/>
+      <c r="F36" s="193"/>
+      <c r="G36" s="193"/>
+      <c r="H36" s="193"/>
+      <c r="I36" s="193"/>
+      <c r="J36" s="194"/>
+      <c r="K36" s="193"/>
+      <c r="L36" s="193"/>
+      <c r="M36" s="193"/>
+      <c r="N36" s="193"/>
+      <c r="O36" s="193"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8830,7 +8827,7 @@
     <col min="2" max="2" width="31.140625" customWidth="1"/>
     <col min="3" max="3" width="34.42578125" customWidth="1"/>
     <col min="4" max="4" width="21.28515625" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
     <col min="6" max="6" width="8.85546875" customWidth="1"/>
     <col min="7" max="7" width="23" customWidth="1"/>
     <col min="8" max="14" width="7.5703125" customWidth="1"/>
@@ -8968,15 +8965,15 @@
       <c r="G6" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="H6" s="237" t="s">
+      <c r="H6" s="221" t="s">
         <v>116</v>
       </c>
-      <c r="I6" s="237"/>
-      <c r="J6" s="237"/>
-      <c r="K6" s="237"/>
-      <c r="L6" s="237"/>
-      <c r="M6" s="237"/>
-      <c r="N6" s="237"/>
+      <c r="I6" s="221"/>
+      <c r="J6" s="221"/>
+      <c r="K6" s="221"/>
+      <c r="L6" s="221"/>
+      <c r="M6" s="221"/>
+      <c r="N6" s="221"/>
       <c r="O6" s="19" t="s">
         <v>117</v>
       </c>
@@ -9334,9 +9331,8 @@
       <c r="D13" s="116" t="s">
         <v>124</v>
       </c>
-      <c r="E13" s="46" t="str">
-        <f>SEC_Comm!C7</f>
-        <v>ELEC_HV</v>
+      <c r="E13" s="46" t="s">
+        <v>308</v>
       </c>
       <c r="F13" s="132">
         <v>1</v>
@@ -9344,7 +9340,7 @@
       <c r="G13" s="61">
         <v>31.536000000000001</v>
       </c>
-      <c r="H13" s="220">
+      <c r="H13" s="217">
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="I13" s="132">
@@ -9365,16 +9361,16 @@
       <c r="N13" s="132">
         <v>0</v>
       </c>
-      <c r="O13" s="221">
+      <c r="O13" s="218">
         <v>0.05</v>
       </c>
-      <c r="P13" s="221">
+      <c r="P13" s="218">
         <v>1</v>
       </c>
-      <c r="Q13" s="221">
+      <c r="Q13" s="218">
         <v>20</v>
       </c>
-      <c r="R13" s="221">
+      <c r="R13" s="218">
         <v>0</v>
       </c>
     </row>
@@ -9390,9 +9386,8 @@
       <c r="D14" s="114" t="s">
         <v>124</v>
       </c>
-      <c r="E14" s="46" t="str">
-        <f>SEC_Comm!C9</f>
-        <v>ELEC_LV</v>
+      <c r="E14" s="46" t="s">
+        <v>306</v>
       </c>
       <c r="F14" s="47">
         <v>1</v>
@@ -9443,7 +9438,7 @@
         <f>SEC_Processes!E14</f>
         <v>Existing Photovoltaics</v>
       </c>
-      <c r="D15" s="222" t="s">
+      <c r="D15" s="219" t="s">
         <v>124</v>
       </c>
       <c r="E15" s="64" t="str">
@@ -9619,16 +9614,16 @@
       <c r="I27" s="65"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B28" s="204" t="s">
+      <c r="B28" s="201" t="s">
         <v>36</v>
       </c>
       <c r="C28" s="42" t="s">
         <v>297</v>
       </c>
-      <c r="D28" s="204" t="s">
+      <c r="D28" s="201" t="s">
         <v>312</v>
       </c>
-      <c r="E28" s="205" t="s">
+      <c r="E28" s="202" t="s">
         <v>38</v>
       </c>
       <c r="F28" s="44"/>
@@ -9655,16 +9650,16 @@
       <c r="I29" s="65"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B30" s="204" t="s">
+      <c r="B30" s="201" t="s">
         <v>36</v>
       </c>
       <c r="C30" s="42" t="s">
         <v>302</v>
       </c>
-      <c r="D30" s="204" t="s">
+      <c r="D30" s="201" t="s">
         <v>333</v>
       </c>
-      <c r="E30" s="205" t="s">
+      <c r="E30" s="202" t="s">
         <v>38</v>
       </c>
       <c r="F30" s="44"/>
@@ -9691,7 +9686,7 @@
       <c r="I31" s="65"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B32" s="204" t="s">
+      <c r="B32" s="201" t="s">
         <v>36</v>
       </c>
       <c r="C32" s="42" t="s">
@@ -9700,7 +9695,7 @@
       <c r="D32" s="42" t="s">
         <v>334</v>
       </c>
-      <c r="E32" s="205" t="s">
+      <c r="E32" s="202" t="s">
         <v>38</v>
       </c>
       <c r="F32" s="44"/>
@@ -9727,7 +9722,7 @@
       <c r="I33" s="65"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B34" s="204" t="s">
+      <c r="B34" s="201" t="s">
         <v>36</v>
       </c>
       <c r="C34" s="42" t="s">
@@ -9736,7 +9731,7 @@
       <c r="D34" s="42" t="s">
         <v>315</v>
       </c>
-      <c r="E34" s="205" t="s">
+      <c r="E34" s="202" t="s">
         <v>38</v>
       </c>
       <c r="F34" s="44"/>
@@ -9763,16 +9758,16 @@
       <c r="I35" s="65"/>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B36" s="204" t="s">
+      <c r="B36" s="201" t="s">
         <v>36</v>
       </c>
       <c r="C36" s="42" t="s">
         <v>328</v>
       </c>
-      <c r="D36" s="204" t="s">
+      <c r="D36" s="201" t="s">
         <v>336</v>
       </c>
-      <c r="E36" s="205" t="s">
+      <c r="E36" s="202" t="s">
         <v>38</v>
       </c>
       <c r="F36" s="44"/>
@@ -9799,16 +9794,16 @@
       <c r="I37" s="65"/>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B38" s="204" t="s">
+      <c r="B38" s="201" t="s">
         <v>36</v>
       </c>
       <c r="C38" s="42" t="s">
         <v>178</v>
       </c>
-      <c r="D38" s="204" t="s">
+      <c r="D38" s="201" t="s">
         <v>179</v>
       </c>
-      <c r="E38" s="205" t="s">
+      <c r="E38" s="202" t="s">
         <v>38</v>
       </c>
       <c r="F38" s="44"/>
@@ -9943,22 +9938,22 @@
       <c r="I45" s="65"/>
     </row>
     <row r="46" spans="2:9" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="215" t="s">
+      <c r="B46" s="212" t="s">
         <v>36</v>
       </c>
-      <c r="C46" s="216" t="s">
+      <c r="C46" s="213" t="s">
         <v>223</v>
       </c>
-      <c r="D46" s="215" t="s">
+      <c r="D46" s="212" t="s">
         <v>223</v>
       </c>
-      <c r="E46" s="217" t="s">
+      <c r="E46" s="214" t="s">
         <v>38</v>
       </c>
-      <c r="F46" s="218"/>
-      <c r="G46" s="218"/>
-      <c r="H46" s="218"/>
-      <c r="I46" s="218"/>
+      <c r="F46" s="215"/>
+      <c r="G46" s="215"/>
+      <c r="H46" s="215"/>
+      <c r="I46" s="215"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9975,7 +9970,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Arkusz7"/>
-  <dimension ref="B2:Q30"/>
+  <dimension ref="B2:Q28"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -10197,149 +10192,115 @@
       <c r="P8" s="118"/>
     </row>
     <row r="9" spans="2:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="185"/>
-      <c r="C9" s="164"/>
-      <c r="D9" s="164" t="s">
-        <v>275</v>
-      </c>
-      <c r="F9" s="186"/>
-      <c r="K9" s="187"/>
-      <c r="P9" s="118"/>
-    </row>
-    <row r="10" spans="2:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="181"/>
-      <c r="C10" s="182"/>
-      <c r="D10" s="182"/>
-      <c r="E10" s="182" t="str">
+      <c r="B9" s="181"/>
+      <c r="C9" s="182"/>
+      <c r="D9" s="182"/>
+      <c r="E9" s="182" t="str">
         <f>SEC_Comm!C11</f>
         <v>ELEC_LV_GRID</v>
       </c>
-      <c r="F10" s="183"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="62"/>
-      <c r="J10" s="62"/>
-      <c r="K10" s="184"/>
-      <c r="L10" s="62"/>
-      <c r="M10" s="62"/>
-      <c r="N10" s="62"/>
-      <c r="O10" s="62"/>
-      <c r="P10" s="118"/>
-    </row>
-    <row r="11" spans="2:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="188" t="str">
+      <c r="F9" s="183"/>
+      <c r="G9" s="62"/>
+      <c r="H9" s="62"/>
+      <c r="I9" s="62"/>
+      <c r="J9" s="62"/>
+      <c r="K9" s="184"/>
+      <c r="L9" s="62"/>
+      <c r="M9" s="62"/>
+      <c r="N9" s="62"/>
+      <c r="O9" s="62"/>
+      <c r="P9" s="118"/>
+    </row>
+    <row r="10" spans="2:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="186" t="str">
         <f>SEC_Processes!D26</f>
         <v>DISTRIBU_LV</v>
       </c>
-      <c r="C11" s="180" t="str">
+      <c r="C10" s="180" t="str">
         <f>SEC_Processes!E26</f>
         <v>Electricity distribution to Low Voltage</v>
       </c>
-      <c r="D11" t="str">
-        <f>SEC_Comm!C9</f>
-        <v>ELEC_LV</v>
-      </c>
-      <c r="F11">
+      <c r="F10">
         <v>0.89</v>
       </c>
-      <c r="G11">
+      <c r="G10">
         <v>5.5</v>
       </c>
-      <c r="H11">
+      <c r="H10">
         <v>1</v>
       </c>
-      <c r="I11">
+      <c r="I10">
         <v>31.536000000000001</v>
       </c>
-      <c r="J11">
+      <c r="J10">
         <v>0</v>
       </c>
-      <c r="K11" s="187">
+      <c r="K10" s="185">
         <v>150</v>
       </c>
-      <c r="L11">
+      <c r="L10">
         <v>150</v>
       </c>
-      <c r="M11">
+      <c r="M10">
         <v>150</v>
       </c>
-      <c r="N11">
+      <c r="N10">
         <v>50</v>
       </c>
-      <c r="O11">
+      <c r="O10">
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="2:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="189"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="62" t="str">
-        <f>SEC_Comm!C11</f>
-        <v>ELEC_LV_GRID</v>
-      </c>
-      <c r="E12" s="62"/>
-      <c r="F12" s="62"/>
-      <c r="G12" s="62"/>
-      <c r="H12" s="62"/>
-      <c r="I12" s="62"/>
-      <c r="J12" s="62"/>
-      <c r="K12" s="184"/>
-      <c r="L12" s="62"/>
-      <c r="M12" s="62"/>
-      <c r="N12" s="62"/>
-      <c r="O12" s="62"/>
-      <c r="P12" s="105"/>
-    </row>
-    <row r="13" spans="2:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="190"/>
-      <c r="C13" s="170"/>
-      <c r="D13" s="170"/>
-      <c r="E13" s="170" t="s">
+    <row r="11" spans="2:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="187"/>
+      <c r="C11" s="170"/>
+      <c r="D11" s="170"/>
+      <c r="E11" s="170" t="s">
         <v>290</v>
       </c>
-      <c r="F13" s="191"/>
-      <c r="G13" s="191"/>
-      <c r="H13" s="191"/>
-      <c r="I13" s="191"/>
-      <c r="J13" s="191"/>
-      <c r="K13" s="192"/>
-      <c r="P13" s="105"/>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
+      <c r="F11" s="188"/>
+      <c r="G11" s="188"/>
+      <c r="H11" s="188"/>
+      <c r="I11" s="188"/>
+      <c r="J11" s="188"/>
+      <c r="K11" s="189"/>
+      <c r="P11" s="105"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="F16" s="163"/>
+      <c r="G16" s="163"/>
+      <c r="H16" s="163"/>
+    </row>
+    <row r="17" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="F17" s="163"/>
+      <c r="G17" s="163"/>
+      <c r="H17" s="163"/>
     </row>
     <row r="18" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="F18" s="163"/>
-      <c r="G18" s="163"/>
-      <c r="H18" s="163"/>
-    </row>
-    <row r="19" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="F19" s="163"/>
-      <c r="G19" s="163"/>
-      <c r="H19" s="163"/>
-    </row>
-    <row r="20" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="F20" s="164"/>
-      <c r="G20" s="164"/>
-      <c r="H20" s="164"/>
+      <c r="F18" s="164"/>
+      <c r="G18" s="164"/>
+      <c r="H18" s="164"/>
+    </row>
+    <row r="26" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D26">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D27">
+        <f>D26/F7</f>
+        <v>106.38297872340426</v>
+      </c>
     </row>
     <row r="28" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D28">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D29">
-        <f>D28/F7</f>
-        <v>106.38297872340426</v>
-      </c>
-    </row>
-    <row r="30" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D30">
-        <f>D29+G7</f>
+        <f>D27+G7</f>
         <v>111.88297872340426</v>
       </c>
     </row>

--- a/VT_Model_ELC_01.xlsx
+++ b/VT_Model_ELC_01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr showObjects="placeholders" codeName="Ten_skoroszyt"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\labee2\Desktop\PIANIFICAZIONE ENERGETICA\myproject_08_05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1760FBB-0A0E-4F23-96FD-51A37009B7BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC27856B-61D0-445A-A9E3-15A30828B6EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" tabRatio="901" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" tabRatio="901" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BALANCE" sheetId="138" r:id="rId1"/>
@@ -1155,7 +1155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="352">
   <si>
     <t>Moc osiągalna elektryczna netto</t>
   </si>
@@ -3526,44 +3526,44 @@
     <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="166" fontId="4" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="3" borderId="27" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4504,10 +4504,10 @@
       <c r="C5" s="69"/>
     </row>
     <row r="6" spans="2:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="B6" s="226" t="s">
+      <c r="B6" s="225" t="s">
         <v>183</v>
       </c>
-      <c r="C6" s="229" t="s">
+      <c r="C6" s="228" t="s">
         <v>136</v>
       </c>
       <c r="D6" s="72" t="s">
@@ -4533,8 +4533,8 @@
       </c>
     </row>
     <row r="7" spans="2:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="B7" s="227"/>
-      <c r="C7" s="230"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="229"/>
       <c r="D7" s="20" t="s">
         <v>137</v>
       </c>
@@ -4558,8 +4558,8 @@
       </c>
     </row>
     <row r="8" spans="2:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B8" s="228"/>
-      <c r="C8" s="231"/>
+      <c r="B8" s="227"/>
+      <c r="C8" s="230"/>
       <c r="D8" s="68" t="s">
         <v>5</v>
       </c>
@@ -4842,10 +4842,10 @@
       <c r="F26" s="69"/>
     </row>
     <row r="27" spans="2:16" ht="31.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="224" t="s">
+      <c r="B27" s="223" t="s">
         <v>213</v>
       </c>
-      <c r="C27" s="222" t="s">
+      <c r="C27" s="221" t="s">
         <v>146</v>
       </c>
       <c r="D27" s="72" t="s">
@@ -4857,8 +4857,8 @@
       <c r="F27" s="69"/>
     </row>
     <row r="28" spans="2:16" ht="31.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="225"/>
-      <c r="C28" s="223"/>
+      <c r="B28" s="224"/>
+      <c r="C28" s="222"/>
       <c r="D28" s="20" t="s">
         <v>149</v>
       </c>
@@ -4985,10 +4985,10 @@
       <c r="F40" s="69"/>
     </row>
     <row r="41" spans="2:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="224" t="s">
+      <c r="B41" s="223" t="s">
         <v>12</v>
       </c>
-      <c r="C41" s="222" t="s">
+      <c r="C41" s="221" t="s">
         <v>146</v>
       </c>
       <c r="D41" s="83" t="s">
@@ -5000,8 +5000,8 @@
       <c r="F41" s="69"/>
     </row>
     <row r="42" spans="2:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="225"/>
-      <c r="C42" s="223"/>
+      <c r="B42" s="224"/>
+      <c r="C42" s="222"/>
       <c r="D42" s="21" t="s">
         <v>24</v>
       </c>
@@ -5250,9 +5250,15 @@
       <c r="O7" s="162">
         <v>30</v>
       </c>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
+      <c r="P7" s="12">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="12">
+        <v>11</v>
+      </c>
+      <c r="R7" s="12">
+        <v>11</v>
+      </c>
       <c r="S7" s="12">
         <v>11</v>
       </c>
@@ -6457,10 +6463,10 @@
       <c r="I43" s="215"/>
     </row>
     <row r="47" spans="2:9" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="232" t="s">
+      <c r="B47" s="231" t="s">
         <v>48</v>
       </c>
-      <c r="C47" s="232"/>
+      <c r="C47" s="231"/>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B48" s="99" t="s">
@@ -7154,11 +7160,11 @@
       <c r="J29" s="130"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B31" s="233" t="s">
+      <c r="B31" s="232" t="s">
         <v>82</v>
       </c>
-      <c r="C31" s="233"/>
-      <c r="D31" s="233"/>
+      <c r="C31" s="232"/>
+      <c r="D31" s="232"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
@@ -7370,15 +7376,15 @@
       <c r="H4" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="I4" s="221" t="s">
+      <c r="I4" s="233" t="s">
         <v>300</v>
       </c>
-      <c r="J4" s="221"/>
-      <c r="K4" s="221"/>
-      <c r="L4" s="221"/>
-      <c r="M4" s="221"/>
-      <c r="N4" s="221"/>
-      <c r="O4" s="221"/>
+      <c r="J4" s="233"/>
+      <c r="K4" s="233"/>
+      <c r="L4" s="233"/>
+      <c r="M4" s="233"/>
+      <c r="N4" s="233"/>
+      <c r="O4" s="233"/>
       <c r="P4" s="19"/>
       <c r="Q4" s="19" t="s">
         <v>203</v>
@@ -8057,15 +8063,15 @@
       <c r="G6" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="H6" s="221" t="s">
+      <c r="H6" s="233" t="s">
         <v>116</v>
       </c>
-      <c r="I6" s="221"/>
-      <c r="J6" s="221"/>
-      <c r="K6" s="221"/>
-      <c r="L6" s="221"/>
-      <c r="M6" s="221"/>
-      <c r="N6" s="221"/>
+      <c r="I6" s="233"/>
+      <c r="J6" s="233"/>
+      <c r="K6" s="233"/>
+      <c r="L6" s="233"/>
+      <c r="M6" s="233"/>
+      <c r="N6" s="233"/>
       <c r="O6" s="19" t="s">
         <v>117</v>
       </c>
@@ -8965,15 +8971,15 @@
       <c r="G6" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="H6" s="221" t="s">
+      <c r="H6" s="233" t="s">
         <v>116</v>
       </c>
-      <c r="I6" s="221"/>
-      <c r="J6" s="221"/>
-      <c r="K6" s="221"/>
-      <c r="L6" s="221"/>
-      <c r="M6" s="221"/>
-      <c r="N6" s="221"/>
+      <c r="I6" s="233"/>
+      <c r="J6" s="233"/>
+      <c r="K6" s="233"/>
+      <c r="L6" s="233"/>
+      <c r="M6" s="233"/>
+      <c r="N6" s="233"/>
       <c r="O6" s="19" t="s">
         <v>117</v>
       </c>
@@ -9441,9 +9447,8 @@
       <c r="D15" s="219" t="s">
         <v>124</v>
       </c>
-      <c r="E15" s="64" t="str">
-        <f>SEC_Comm!C8</f>
-        <v>ELEC_MV</v>
+      <c r="E15" s="64" t="s">
+        <v>308</v>
       </c>
       <c r="F15" s="84">
         <v>1</v>
@@ -10220,6 +10225,9 @@
         <f>SEC_Processes!E26</f>
         <v>Electricity distribution to Low Voltage</v>
       </c>
+      <c r="D10" t="s">
+        <v>306</v>
+      </c>
       <c r="F10">
         <v>0.89</v>
       </c>
@@ -10562,6 +10570,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="154c1c0f-2c06-4f37-a5b1-faba3524bf7f">
@@ -10570,15 +10587,6 @@
     <TaxCatchAll xmlns="0be4b9af-ad17-4489-a21e-b8b210aeb5f9" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10777,6 +10785,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A551C1B6-05FC-4B61-8034-B37F3A0576E1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CA861A5-7E6A-41A7-8E0B-DCD15A12B5CB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -10785,14 +10801,6 @@
     <ds:schemaRef ds:uri="833e474d-e424-4496-95f1-98e7780be11a"/>
     <ds:schemaRef ds:uri="154c1c0f-2c06-4f37-a5b1-faba3524bf7f"/>
     <ds:schemaRef ds:uri="0be4b9af-ad17-4489-a21e-b8b210aeb5f9"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A551C1B6-05FC-4B61-8034-B37F3A0576E1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
